--- a/Time and Cost experiment/Experiment/cleaned_project_risk_dataset_UPDATED.xlsx
+++ b/Time and Cost experiment/Experiment/cleaned_project_risk_dataset_UPDATED.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cacb9c3f838fb654/Skrivbord/SPM/Time and Cost experiment/Experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4C48824-A98B-4908-B6F8-949FE8E006B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{C4C48824-A98B-4908-B6F8-949FE8E006B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39F31751-CD65-4618-96D4-8747D047A210}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activities" sheetId="1" r:id="rId1"/>
@@ -76,9 +76,6 @@
     <t>Duration_Max_Days</t>
   </si>
   <si>
-    <t>Variable_Cost_per_Day_x1000</t>
-  </si>
-  <si>
     <t>Source_Excel_Row</t>
   </si>
   <si>
@@ -490,9 +487,6 @@
     <t>0.10-0.30</t>
   </si>
   <si>
-    <t>Uniforme</t>
-  </si>
-  <si>
     <t>B</t>
   </si>
   <si>
@@ -589,28 +583,34 @@
     <t>Cost_Most_Likely_x1000</t>
   </si>
   <si>
-    <t>Cost_Min_Days_x1000</t>
-  </si>
-  <si>
-    <t>Cost_Max_Days_x1000</t>
-  </si>
-  <si>
     <t>Cost_Distribution</t>
   </si>
   <si>
     <t>PERT</t>
   </si>
   <si>
-    <t>Variable_Cost_Min_Days_x1000</t>
-  </si>
-  <si>
     <t>Variable_Cost_Max_Days_x1000</t>
   </si>
   <si>
     <t>Variable_Cost_Distribution</t>
   </si>
   <si>
-    <t>DiscreteUniforme</t>
+    <t>Uniform</t>
+  </si>
+  <si>
+    <t>DiscreteUniform</t>
+  </si>
+  <si>
+    <t>Cost_Min_x1000</t>
+  </si>
+  <si>
+    <t>Cost_Max_x1000</t>
+  </si>
+  <si>
+    <t>Variable_Cost_Min_x1000</t>
+  </si>
+  <si>
+    <t>Variable_Cost_per_x1000</t>
   </si>
 </sst>
 </file>
@@ -701,10 +701,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1014,9 +1010,9 @@
     <col min="16" max="16" width="22.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="22.109375" style="1" customWidth="1"/>
     <col min="18" max="18" width="16.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="29.6640625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="22.109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="18.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1058,51 +1054,51 @@
         <v>11</v>
       </c>
       <c r="M1" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="O1" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="U1" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="T1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J2" s="1">
         <v>10</v>
@@ -1117,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O2" s="1">
         <f>P2*0.75</f>
@@ -1131,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S2" s="1">
         <f>T2*0.75</f>
@@ -1150,31 +1146,31 @@
     </row>
     <row r="3" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J3" s="1">
         <v>25</v>
@@ -1189,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O3" s="1">
         <f t="shared" ref="O3:O33" si="0">P3*0.75</f>
@@ -1203,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S3" s="1">
         <f t="shared" ref="S3:S33" si="2">T3*0.75</f>
@@ -1222,19 +1218,19 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J4" s="1">
         <v>20</v>
@@ -1249,7 +1245,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O4" s="1">
         <f t="shared" si="0"/>
@@ -1263,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S4" s="1">
         <f t="shared" si="2"/>
@@ -1282,19 +1278,19 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1">
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J5" s="1">
         <v>45</v>
@@ -1309,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O5" s="1">
         <f t="shared" si="0"/>
@@ -1323,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S5" s="1">
         <f t="shared" si="2"/>
@@ -1342,19 +1338,19 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1">
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J6" s="1">
         <v>60</v>
@@ -1369,7 +1365,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O6" s="1">
         <f t="shared" si="0"/>
@@ -1383,7 +1379,7 @@
         <v>0</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S6" s="1">
         <f t="shared" si="2"/>
@@ -1402,28 +1398,28 @@
     </row>
     <row r="7" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1">
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J7" s="1">
         <v>80</v>
@@ -1438,7 +1434,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O7" s="1">
         <f t="shared" si="0"/>
@@ -1452,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S7" s="1">
         <f t="shared" si="2"/>
@@ -1471,19 +1467,19 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1">
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J8" s="1">
         <v>50</v>
@@ -1498,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O8" s="1">
         <f t="shared" si="0"/>
@@ -1512,7 +1508,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S8" s="1">
         <f t="shared" si="2"/>
@@ -1531,28 +1527,28 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" s="1">
         <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J9" s="1">
         <v>20</v>
@@ -1567,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O9" s="1">
         <f t="shared" si="0"/>
@@ -1581,7 +1577,7 @@
         <v>813.125</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S9" s="1">
         <f t="shared" si="2"/>
@@ -1600,19 +1596,19 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="1">
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J10" s="1">
         <v>70</v>
@@ -1627,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O10" s="1">
         <f t="shared" si="0"/>
@@ -1641,7 +1637,7 @@
         <v>5250</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S10" s="1">
         <f t="shared" si="2"/>
@@ -1660,19 +1656,19 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="1">
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J11" s="1">
         <v>70</v>
@@ -1687,7 +1683,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O11" s="1">
         <f t="shared" si="0"/>
@@ -1701,7 +1697,7 @@
         <v>4593.75</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S11" s="1">
         <f t="shared" si="2"/>
@@ -1720,19 +1716,19 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1">
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J12" s="1">
         <v>70</v>
@@ -1747,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O12" s="1">
         <f t="shared" si="0"/>
@@ -1761,7 +1757,7 @@
         <v>8750</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S12" s="1">
         <f t="shared" si="2"/>
@@ -1780,28 +1776,28 @@
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1">
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J13" s="1">
         <v>100</v>
@@ -1816,7 +1812,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O13" s="1">
         <f t="shared" si="0"/>
@@ -1830,7 +1826,7 @@
         <v>93.75</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S13" s="1">
         <f t="shared" si="2"/>
@@ -1849,31 +1845,31 @@
     </row>
     <row r="14" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" s="1">
         <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J14" s="1">
         <v>70</v>
@@ -1888,7 +1884,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O14" s="1">
         <f t="shared" si="0"/>
@@ -1902,7 +1898,7 @@
         <v>625</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S14" s="1">
         <f t="shared" si="2"/>
@@ -1921,19 +1917,19 @@
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="1">
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J15" s="1">
         <v>25</v>
@@ -1948,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O15" s="1">
         <f t="shared" si="0"/>
@@ -1962,7 +1958,7 @@
         <v>125</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S15" s="1">
         <f t="shared" si="2"/>
@@ -1981,19 +1977,19 @@
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16" s="1">
         <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J16" s="1">
         <v>12</v>
@@ -2008,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O16" s="1">
         <f t="shared" si="0"/>
@@ -2022,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S16" s="1">
         <f t="shared" si="2"/>
@@ -2041,19 +2037,19 @@
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" s="1">
         <v>16</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J17" s="1">
         <v>170</v>
@@ -2068,7 +2064,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O17" s="1">
         <f t="shared" si="0"/>
@@ -2082,7 +2078,7 @@
         <v>375</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S17" s="1">
         <f t="shared" si="2"/>
@@ -2101,19 +2097,19 @@
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" s="1">
         <v>17</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J18" s="1">
         <v>45</v>
@@ -2128,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O18" s="1">
         <f t="shared" si="0"/>
@@ -2142,7 +2138,7 @@
         <v>375</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S18" s="1">
         <f t="shared" si="2"/>
@@ -2161,19 +2157,19 @@
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" s="1">
         <v>18</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J19" s="1">
         <v>50</v>
@@ -2188,7 +2184,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O19" s="1">
         <f t="shared" si="0"/>
@@ -2202,7 +2198,7 @@
         <v>687.5</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S19" s="1">
         <f t="shared" si="2"/>
@@ -2221,19 +2217,19 @@
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" s="1">
         <v>19</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J20" s="1">
         <v>45</v>
@@ -2248,7 +2244,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O20" s="1">
         <f t="shared" si="0"/>
@@ -2262,7 +2258,7 @@
         <v>718.75</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S20" s="1">
         <f t="shared" si="2"/>
@@ -2281,28 +2277,28 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" s="1">
         <v>20</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J21" s="1">
         <v>80</v>
@@ -2317,7 +2313,7 @@
         <v>0</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O21" s="1">
         <f t="shared" si="0"/>
@@ -2331,7 +2327,7 @@
         <v>843.75</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S21" s="1">
         <f t="shared" si="2"/>
@@ -2350,19 +2346,19 @@
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" s="1">
         <v>21</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J22" s="1">
         <v>20</v>
@@ -2377,7 +2373,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O22" s="1">
         <f t="shared" si="0"/>
@@ -2391,7 +2387,7 @@
         <v>343.75</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S22" s="1">
         <f t="shared" si="2"/>
@@ -2410,19 +2406,19 @@
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" s="1">
         <v>22</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J23" s="1">
         <v>18</v>
@@ -2437,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O23" s="1">
         <f t="shared" si="0"/>
@@ -2451,7 +2447,7 @@
         <v>343.75</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S23" s="1">
         <f t="shared" si="2"/>
@@ -2470,28 +2466,28 @@
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" s="1">
         <v>23</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J24" s="1">
         <v>35</v>
@@ -2506,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O24" s="1">
         <f t="shared" si="0"/>
@@ -2520,7 +2516,7 @@
         <v>358.75</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S24" s="1">
         <f t="shared" si="2"/>
@@ -2539,19 +2535,19 @@
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25" s="1">
         <v>24</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J25" s="1">
         <v>30</v>
@@ -2566,7 +2562,7 @@
         <v>0</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O25" s="1">
         <f t="shared" si="0"/>
@@ -2580,7 +2576,7 @@
         <v>343.75</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S25" s="1">
         <f t="shared" si="2"/>
@@ -2599,19 +2595,19 @@
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="1">
         <v>25</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J26" s="1">
         <v>35</v>
@@ -2626,7 +2622,7 @@
         <v>0</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O26" s="1">
         <f t="shared" si="0"/>
@@ -2640,7 +2636,7 @@
         <v>93.75</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S26" s="1">
         <f t="shared" si="2"/>
@@ -2659,31 +2655,31 @@
     </row>
     <row r="27" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="1">
         <v>26</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J27" s="1">
         <v>75</v>
@@ -2698,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O27" s="1">
         <f t="shared" si="0"/>
@@ -2712,7 +2708,7 @@
         <v>156.25</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S27" s="1">
         <f t="shared" si="2"/>
@@ -2731,19 +2727,19 @@
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="1">
         <v>27</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J28" s="1">
         <v>75</v>
@@ -2758,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O28" s="1">
         <f t="shared" si="0"/>
@@ -2772,7 +2768,7 @@
         <v>125</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S28" s="1">
         <f t="shared" si="2"/>
@@ -2791,28 +2787,28 @@
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29" s="1">
         <v>28</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J29" s="1">
         <v>45</v>
@@ -2827,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O29" s="1">
         <f t="shared" si="0"/>
@@ -2841,7 +2837,7 @@
         <v>468.75</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S29" s="1">
         <f t="shared" si="2"/>
@@ -2860,19 +2856,19 @@
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B30" s="1">
         <v>29</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J30" s="1">
         <v>12</v>
@@ -2887,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O30" s="1">
         <f t="shared" si="0"/>
@@ -2901,7 +2897,7 @@
         <v>0</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S30" s="1">
         <f t="shared" si="2"/>
@@ -2920,31 +2916,31 @@
     </row>
     <row r="31" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B31" s="1">
         <v>30</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J31" s="1">
         <v>50</v>
@@ -2959,7 +2955,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O31" s="1">
         <f t="shared" si="0"/>
@@ -2973,7 +2969,7 @@
         <v>93.75</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S31" s="1">
         <f t="shared" si="2"/>
@@ -2992,28 +2988,28 @@
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B32" s="1">
         <v>31</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J32" s="1">
         <v>12</v>
@@ -3028,7 +3024,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O32" s="1">
         <f t="shared" si="0"/>
@@ -3042,7 +3038,7 @@
         <v>0</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S32" s="1">
         <f t="shared" si="2"/>
@@ -3061,19 +3057,19 @@
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B33" s="1">
         <v>32</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J33" s="1">
         <v>12</v>
@@ -3088,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O33" s="1">
         <f t="shared" si="0"/>
@@ -3102,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S33" s="1">
         <f t="shared" si="2"/>
@@ -3160,120 +3156,120 @@
   <sheetData>
     <row r="1" spans="1:29" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="J2" s="1">
         <v>2</v>
@@ -3285,13 +3281,13 @@
         <v>0.03</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="O2" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P2" s="1">
         <v>5</v>
@@ -3300,7 +3296,7 @@
         <v>20</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="S2" s="1">
         <v>2</v>
@@ -3312,19 +3308,19 @@
         <v>20</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="W2" s="1">
         <v>2</v>
       </c>
       <c r="X2" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y2" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="Y2" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="AA2" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AB2" s="1">
         <v>42</v>
@@ -3335,31 +3331,31 @@
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="J3" s="1">
         <v>2</v>
@@ -3371,13 +3367,13 @@
         <v>0.5</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P3" s="1">
         <v>20</v>
@@ -3386,7 +3382,7 @@
         <v>50</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="S3" s="1">
         <v>2</v>
@@ -3398,19 +3394,19 @@
         <v>50</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="W3" s="1">
         <v>6</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AB3" s="1">
         <v>44</v>
@@ -3421,31 +3417,31 @@
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="J4" s="1">
         <v>2</v>
@@ -3457,13 +3453,13 @@
         <v>0.1</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="P4" s="1">
         <v>50</v>
@@ -3472,7 +3468,7 @@
         <v>75</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="S4" s="1">
         <v>2</v>
@@ -3484,19 +3480,19 @@
         <v>75</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="W4" s="1">
         <v>9</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AB4" s="1">
         <v>46</v>
@@ -3507,31 +3503,31 @@
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="J5" s="1">
         <v>2</v>
@@ -3543,13 +3539,13 @@
         <v>0.3</v>
       </c>
       <c r="M5" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="N5" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="O5" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P5" s="1">
         <v>5</v>
@@ -3558,7 +3554,7 @@
         <v>20</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="S5" s="1">
         <v>2</v>
@@ -3570,16 +3566,16 @@
         <v>20</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="W5" s="1">
         <v>12</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AB5" s="1">
         <v>48</v>
@@ -3590,31 +3586,31 @@
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="J6" s="1">
         <v>2</v>
@@ -3626,13 +3622,13 @@
         <v>0.3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P6" s="1">
         <v>20</v>
@@ -3641,7 +3637,7 @@
         <v>50</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="S6" s="1">
         <v>2</v>
@@ -3653,16 +3649,16 @@
         <v>50</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="W6" s="1">
         <v>28</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AA6" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AB6" s="1">
         <v>50</v>
@@ -3673,31 +3669,31 @@
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="J7" s="1">
         <v>2</v>
@@ -3709,13 +3705,13 @@
         <v>0.1</v>
       </c>
       <c r="M7" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="N7" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="O7" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P7" s="1">
         <v>5</v>
@@ -3724,7 +3720,7 @@
         <v>20</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="S7" s="1">
         <v>2</v>
@@ -3736,19 +3732,19 @@
         <v>20</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="W7" s="1">
         <v>26</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AB7" s="1">
         <v>52</v>
@@ -3759,31 +3755,31 @@
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="J8" s="1">
         <v>2</v>
@@ -3795,13 +3791,13 @@
         <v>0.03</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P8" s="1">
         <v>20</v>
@@ -3810,7 +3806,7 @@
         <v>50</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="S8" s="1">
         <v>2</v>
@@ -3822,16 +3818,16 @@
         <v>50</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="W8" s="1">
         <v>30</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AB8" s="1">
         <v>54</v>
@@ -3842,31 +3838,31 @@
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="J9" s="1">
         <v>2</v>
@@ -3878,13 +3874,13 @@
         <v>0.3</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P9" s="1">
         <v>20</v>
@@ -3893,7 +3889,7 @@
         <v>50</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="S9" s="1">
         <v>2</v>
@@ -3905,16 +3901,16 @@
         <v>50</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="W9" s="1">
         <v>23</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AA9" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AB9" s="1">
         <v>56</v>
@@ -3925,31 +3921,31 @@
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="J10" s="1">
         <v>2</v>
@@ -3961,13 +3957,13 @@
         <v>0.1</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P10" s="1">
         <v>20</v>
@@ -3976,7 +3972,7 @@
         <v>50</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="S10" s="1">
         <v>2</v>
@@ -3988,16 +3984,16 @@
         <v>20</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="W10" s="1">
         <v>20</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AA10" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AB10" s="1">
         <v>58</v>
@@ -4008,31 +4004,31 @@
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="J11" s="1">
         <v>2</v>
@@ -4044,13 +4040,13 @@
         <v>0.5</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="P11" s="1">
         <v>100</v>
@@ -4059,7 +4055,7 @@
         <v>750</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="S11" s="1">
         <v>2</v>
@@ -4071,22 +4067,22 @@
         <v>750</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="W11" s="1">
         <v>2</v>
       </c>
       <c r="X11" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="Y11" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="Y11" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="Z11" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AA11" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AB11" s="1">
         <v>60</v>
@@ -4097,31 +4093,31 @@
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="J12" s="1">
         <v>2</v>
@@ -4133,13 +4129,13 @@
         <v>0.1</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="P12" s="1">
         <v>750</v>
@@ -4148,7 +4144,7 @@
         <v>2500</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="S12" s="1">
         <v>2</v>
@@ -4160,16 +4156,16 @@
         <v>2500</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="W12" s="1">
         <v>8</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AB12" s="1">
         <v>62</v>
@@ -4180,31 +4176,31 @@
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="J13" s="1">
         <v>2</v>
@@ -4216,13 +4212,13 @@
         <v>0.1</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="P13" s="1">
         <v>100</v>
@@ -4231,7 +4227,7 @@
         <v>750</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="S13" s="1">
         <v>2</v>
@@ -4243,22 +4239,22 @@
         <v>750</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="W13" s="1">
         <v>13</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AA13" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AB13" s="1">
         <v>64</v>
@@ -4269,31 +4265,31 @@
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="J14" s="1">
         <v>2</v>
@@ -4305,13 +4301,13 @@
         <v>0.1</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="P14" s="1">
         <v>750</v>
@@ -4320,7 +4316,7 @@
         <v>2500</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="S14" s="1">
         <v>2</v>
@@ -4332,22 +4328,22 @@
         <v>2500</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="W14" s="1">
         <v>26</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AA14" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AB14" s="1">
         <v>66</v>
@@ -4358,31 +4354,31 @@
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="J15" s="1">
         <v>2</v>
@@ -4394,13 +4390,13 @@
         <v>0.03</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="P15" s="1">
         <v>0</v>
@@ -4409,7 +4405,7 @@
         <v>100</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="S15" s="1">
         <v>2</v>
@@ -4421,19 +4417,19 @@
         <v>100</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="W15" s="1">
         <v>30</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AA15" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AB15" s="1">
         <v>68</v>
@@ -4444,31 +4440,31 @@
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="J16" s="1">
         <v>2</v>
@@ -4480,13 +4476,13 @@
         <v>0.1</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="P16" s="1">
         <v>2500</v>
@@ -4495,7 +4491,7 @@
         <v>6000</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="S16" s="1">
         <v>2</v>
@@ -4507,16 +4503,16 @@
         <v>6000</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="W16" s="1">
         <v>31</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AB16" s="1">
         <v>70</v>
